--- a/AAII_Financials/Quarterly/BMO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BMO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>BMO</t>
   </si>
@@ -656,272 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6539500</v>
+      </c>
+      <c r="E8" s="3">
         <v>6485400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6692700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6126800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5918600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5518100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5703700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5334800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5274600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5288900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5265800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5668600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5747300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4989300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8370300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6649200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5205400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4015300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3784800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3724400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3625900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3680000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3801600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3980900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4218100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4830400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5114600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5209800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5324300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4936900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4883000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4271500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4102700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3727800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3538700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3091400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2979100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2900100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2937700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2858600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1042,53 +1048,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6539500</v>
+      </c>
+      <c r="E10" s="3">
         <v>6485400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6692700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6126800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5918600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5518100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5703700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5334800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5274600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5288900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5265800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5668600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5747300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4989300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1164,8 +1173,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1330,8 +1343,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,8 +1468,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1496,8 +1515,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1574,130 +1593,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>397800</v>
+      </c>
+      <c r="E15" s="3">
         <v>400400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>403300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>185900</v>
       </c>
-      <c r="G15" s="3">
-        <v>385100</v>
-      </c>
       <c r="H15" s="3">
+        <v>385900</v>
+      </c>
+      <c r="I15" s="3">
         <v>393700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>376600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>185100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>383700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>381300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>397600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>186100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>418100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>415900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-119200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-113700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-111600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-106900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-109100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-120700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-116300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-118600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-117100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-123000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-118100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-122500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-118500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-115400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-107100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-106200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-102400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-90800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-94900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-97100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-91500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-94500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-87100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-93700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-91400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-85300</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4545000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3698200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4024600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3757700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3487800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3418000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3550700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2976000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3302600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3323600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3819400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3884400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4020000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3851500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5570100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4068700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2204400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1214800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>791000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>848900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>965900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1130800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1232200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1713900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1742600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2206800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2728800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2784200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3015900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2659000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2546600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2207700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2073200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1841300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1504000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1355200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1187800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1248400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1127000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1073200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1994500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2787200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2668100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2369100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2430700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2100100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2153000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2358800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1972000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1965200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1446300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1784200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1727200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1137800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2800200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2580500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3001000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2800400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2993800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2875600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2660000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2549200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2569400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2267100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2475500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2623600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2385800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2425600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2308500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2277900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2336400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2063800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2029500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1886500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2034700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1736200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1791300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1651700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1810700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1785400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,252 +2057,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>215300</v>
+      </c>
+      <c r="E20" s="3">
         <v>217500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>216700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>206900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>214200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>199000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>208500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>204500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>215900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>205000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2432100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1746100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1751400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1825500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-162100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-802200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-464400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1130000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-613500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-714900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1324000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1974400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-805500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1246700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-736700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-829900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-876100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-512300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-539000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-709900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-742700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-616200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-456200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-500900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-390300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-477800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2970100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2854600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2348000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2615000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2615700</v>
+      </c>
+      <c r="I21" s="3">
         <v>2279600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2330500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2343000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2155200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2145700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1635400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1765800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1929400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1348700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>651500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4602800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1520800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4888400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3102900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2344400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2456300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1685700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2220300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1832200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1421400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>929500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1855100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1379200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1766100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1639700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1643600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1718600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1660700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1347500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1455700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1291900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1492900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1318300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1585600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1468100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2313,8 +2352,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2391,252 +2430,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1779200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2569800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2451300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2162200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2229800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1885900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1954000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2157900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1771500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1764400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1237800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1579700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1511300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>932800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>368100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4326600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1249600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4626000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2831700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2073300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2195600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1419100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1956000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1552100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1151500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>649200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1580300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1178900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1571800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1448000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1460300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1551500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1490500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1176600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1291900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1120000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1335100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1150800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1420500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1307500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E24" s="3">
         <v>637700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>616300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>524500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>546300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>466100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>476700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>504500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>421300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>406700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>272100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>348500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>321600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>174000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>270200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1059600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>240900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1168300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>699400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>474100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>510400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>440800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>441500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>326500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>207000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>108300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>330500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>247900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>337000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>295600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>297900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>318300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>333500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>238600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>251500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>206900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>302900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>192100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>277300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>274300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1932100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1835000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1637700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1683600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1419900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1477200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1653400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1350100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1357700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>965700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1231200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1189700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>758800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>97900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3267000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1008700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3457700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2132300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1599300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1685200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>978400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1514500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1225600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>944500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>540900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1249800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>930900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1234700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1152400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1162400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1233200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1157000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>938000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1040400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>913100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1032200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>958800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1143100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1033300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1188300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1827000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1776000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1516400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1633700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1315700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1429500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1542200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1313200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1250700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>934300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1136200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1157100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>662900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>69900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3210900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>974000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3419900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2092300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1555600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1640000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>927300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1472400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1185400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>888500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>500100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1194800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>890400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1187900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1115500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1122400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1201900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1119400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>903300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1006900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>877400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>995800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>925700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1107800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1006400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3269,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3218,21 +3278,21 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-316300</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,252 +3555,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-215300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-217500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-216700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-206900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-214200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-199000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-208500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-204500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-215900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-205000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2432100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1746100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1751400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1825500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>162100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>802200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>464400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1130000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>613500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>714900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1324000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1974400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>805500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1246700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>736700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>829900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>876100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>512300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>539000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>709900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>742700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>616200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>456200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>500900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>390300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>477800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1929200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1835700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1632700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1681400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1418400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1474500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1651200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1350100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1354800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>964200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1226200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1188200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>756600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>69900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3210900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>974000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3419900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2092300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1555600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1640000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>927300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1472400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1185400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>888500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>500100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1194800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>890400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1187900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1115500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1122400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1201900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1119400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>903300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>690600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>877400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>995800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>925700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1107800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1006400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1929200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1835700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1632700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1681400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1418400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1474500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1651200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1350100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1354800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>964200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1226200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1188200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>756600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>69900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3210900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>974000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3419900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2092300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1555600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1640000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>927300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1472400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1185400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>888500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>500100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1194800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>890400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1187900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1115500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1122400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1201900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1119400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>903300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>690600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>877400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>995800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>925700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1107800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1006400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,297 +4277,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52766800</v>
+      </c>
+      <c r="E41" s="3">
         <v>46843300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49609600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48078300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42279700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47242000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52764800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46658100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>54060900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58058100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>55719800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>56022800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>61701700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50431700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76071100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>63741700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>51423400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51098600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>36439900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>69082200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>62092500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>74029500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>54881100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44419400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>58717000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>56204100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>35909800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38050200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>30878600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27589600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>31154600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>61248300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>30918600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>27041700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>30630900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>48521000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>24241900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>27293700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>26180500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>24316800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>274460900</v>
+      </c>
+      <c r="E42" s="3">
         <v>287126300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>278535300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>272383700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>254167400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>250623800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>241653800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>237334800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>236366400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>232436000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>214205200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>204096100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>209708800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>202705500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>186610500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>176388300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>178202300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>166510700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>189426100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>174400600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>171130900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>159357300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>183102500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>180515900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>177293200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>176310500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>176639400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>165634700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>176667400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>179060100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>171528200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>149237400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>158128100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>152888600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>205986900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>156668900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>156934500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>162576700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>156135800</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>150292700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34139300</v>
+      </c>
+      <c r="E43" s="3">
         <v>38350200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>34933400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40162600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>32321300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36199400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27749400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31370600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24337400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25483100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1299100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46747000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1463400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1568500</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4558,8 +4650,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4602,8 +4697,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4680,53 +4775,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1020800</v>
+      </c>
+      <c r="E45" s="3">
         <v>877900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>797000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8257600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>325200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>317000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>360000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10267000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>358400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2771400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5324100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12174600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7263100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7809800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>362431300</v>
+      </c>
+      <c r="E46" s="3">
         <v>373240200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>363939400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>376914900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>329147000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>334441500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>322592300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>332447100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>315184600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>318802400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>276631900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>326286600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>280212300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>262592300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,53 +5025,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>180920500</v>
+      </c>
+      <c r="E47" s="3">
         <v>174184900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>166259500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>166235400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>162351200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>163650800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>157398200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>164823100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>158915700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>152388000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>157093600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>142436400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>142335800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>145176300</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5046,252 +5150,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4512900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4532000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4526700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4479200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4468400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4458600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4361200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4532500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4523900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4555400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4637900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4582800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4570400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4506300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3581200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3527900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3402300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3330400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3307900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3299300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3160000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3227200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3155100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3236600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2975300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3119000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3106400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1602200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1577300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1526600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1517300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1443200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1448400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1480000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1462400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1513000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1464600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1587900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1584100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1649400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15143200</v>
+      </c>
+      <c r="E49" s="3">
         <v>15896800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15949500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15381300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15550400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15525900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15537100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15571600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15638600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15713800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15833100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15799800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15990500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15620400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5548100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5449700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5265300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5156000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5109400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5662200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5739300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5780100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6572300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6946000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6927400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7309600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6928900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6833000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6858000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6798300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6676600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6282200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6385200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6363300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>6102500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>6253600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6077200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>6732000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>6442400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6575300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35071700</v>
+      </c>
+      <c r="E52" s="3">
         <v>33090200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29750600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5649400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31631200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>33314800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>36598200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5486900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29853800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27764100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>53817600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5480700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24301900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24683800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1326500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>856300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>586800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>571400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>746600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>953300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>895600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>971600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1005400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1139700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1116200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1092000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1226200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1222500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1318000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1358700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1395700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1481700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1554500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1625300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1629800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2132200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2083000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2435300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2254000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2382300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1096812200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1101616900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1074993500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1053819800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1034396500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1042298600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1014359700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1011587400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1013856200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>999747500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>990187500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>969850500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>949174800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>922411200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>873752300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>830202700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>789491100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>757228200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>743856300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>731980700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>719523700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>713196100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>730745200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>734490700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>746330200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>774896900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>690624200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>664430900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>665486500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>639312400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>620934500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>561944300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>576123700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>559751300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>541735000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>528076500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>527359900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>552313600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>531910200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>528492300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,58 +6117,59 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>672903400</v>
+      </c>
+      <c r="E57" s="3">
         <v>660107800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>657038800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>657330600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>690316100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>693481800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>688748100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>656831000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>698775100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>682168200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>683268400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>605951600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>671706200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>645554600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -6110,297 +6240,306 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>49610400</v>
+      </c>
+      <c r="E58" s="3">
         <v>47057800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>145564400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>179570900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>128769100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>130202900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>132425700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>160185900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>128970600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>125537700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>112204300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>153108300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>110436300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>111738000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>144085400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>110426100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>108716500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>102759200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>109145300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>99294700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>93302100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>95518400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>104947700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>95620800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>104122700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>109797900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>103659600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>91743800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>96406600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>94841800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>93470000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>72081100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>84058800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>81424800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>76992200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>62457800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>67940400</v>
       </c>
-      <c r="AN58" s="3">
-        <v>0</v>
-      </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38002800</v>
+      </c>
+      <c r="E59" s="3">
         <v>47660200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>50514200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46425700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>50390500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>51312800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42275700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30930000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40907000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>45911700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>78979600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42502600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42569200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41215700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>147200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>309700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>171400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>139600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>163700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>114100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>144900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>147200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>97500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>42900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>69100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>42900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>25400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>32300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>64700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>36300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>35400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>38700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>93000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>23800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>32300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>69900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>62200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>796831500</v>
+      </c>
+      <c r="E60" s="3">
         <v>796489900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>885065700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>920253600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>903000100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>910264000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>891974100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>878330800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>893646700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>881446400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>874452300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>845111900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>824711700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>798508200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,252 +6615,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>191911600</v>
+      </c>
+      <c r="E61" s="3">
         <v>195343900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>95120900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52160000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41927800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42288400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36360600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54681700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30554600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30355100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25716600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45910400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21958900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21684100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25389900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20867300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20086500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20136000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20537300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20711100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19577000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19396200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20402400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>24889200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>25070700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26443600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>24909600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22916800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22248200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>21890600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>21217000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20441800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>19105800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18988400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22301000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18188500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>17331200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3317200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3357200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3410200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46357800</v>
+      </c>
+      <c r="E62" s="3">
         <v>46885900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31587800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17787500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26774800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27630200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25499000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17334100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29599000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30051700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32256800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23286400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46100500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46113500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>100100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>74300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>59900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>80000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>142200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>139300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>122400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>116400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>62900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>51000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>47900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>46800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>58700</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>56200</v>
       </c>
       <c r="AG62" s="3">
         <v>56200</v>
       </c>
       <c r="AH62" s="3">
+        <v>56200</v>
+      </c>
+      <c r="AI62" s="3">
         <v>53800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>139300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>154100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>173400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>172700</v>
-      </c>
-      <c r="AN62" s="3">
-        <v>187400</v>
       </c>
       <c r="AO62" s="3">
         <v>187400</v>
       </c>
       <c r="AP62" s="3">
+        <v>187400</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>185900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1035100900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1038719700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1011774500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>990953200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>971702700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>980182700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>953833700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>951102300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>953800300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>941853200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>932425700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>915041600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>892771100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>866305800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>819408200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>778433000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>739983200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>709542100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700378200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>689371200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>676786000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>671512900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>688585900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>690701900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>704481600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>731535500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>649663400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>624608500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>625325600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>601287200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>584484300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>528719300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>542431900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>526819800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>509868700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>495067800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>495407900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>517810100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>499293400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>495993100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,112 +7660,115 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1104900</v>
+      </c>
+      <c r="E70" s="3">
         <v>1138700</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1142700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1106100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1264500</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1266400</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1209100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>1471100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>4370400</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>3648100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2466600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2376000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>2508700</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>2433400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>7551000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1931200</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>2253900</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>2217400</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>2653600</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>2703700</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>2918500</v>
-      </c>
-      <c r="X70" s="3">
-        <v>2958400</v>
       </c>
       <c r="Y70" s="3">
         <v>2958400</v>
       </c>
       <c r="Z70" s="3">
+        <v>2958400</v>
+      </c>
+      <c r="AA70" s="3">
         <v>3628900</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>3595500</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>3681900</v>
       </c>
       <c r="AC70" s="3">
         <v>3681900</v>
       </c>
       <c r="AD70" s="3">
+        <v>3681900</v>
+      </c>
+      <c r="AE70" s="3">
         <v>3656700</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>3719300</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>3610500</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>3341000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>3153800</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>3191800</v>
       </c>
       <c r="AJ70" s="3">
         <v>3191800</v>
       </c>
       <c r="AK70" s="3">
-        <v>3155500</v>
+        <v>3191800</v>
       </c>
       <c r="AL70" s="3">
         <v>3155500</v>
@@ -7610,16 +7777,19 @@
         <v>3155500</v>
       </c>
       <c r="AN70" s="3">
+        <v>3155500</v>
+      </c>
+      <c r="AO70" s="3">
         <v>3334100</v>
-      </c>
-      <c r="AO70" s="3">
-        <v>2950000</v>
       </c>
       <c r="AP70" s="3">
         <v>2950000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>2950000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34026000</v>
+      </c>
+      <c r="E72" s="3">
         <v>35301400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35179600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>33807400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34361100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34127500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32641900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33347000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32903800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>32575700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33007900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31684500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33829800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>32551200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31763100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>32879500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>30781200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>30007300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27272300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>26294000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>25251100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>24448800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>24036500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23788900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22924100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>23100900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23166800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22396000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22395700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21096900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20476400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18784900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18751200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18156500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>17781400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>17644500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>17253000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>17441100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>16960200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>16290300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>60570800</v>
+      </c>
+      <c r="E76" s="3">
         <v>61724000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62042500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>61725600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>61398900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60822000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59288600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58988200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>55663000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54223700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>55273600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52412700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53879000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53657900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46793000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49838400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>47254000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45468700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>40824500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>39905900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39819200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>38724900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39200900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>40159900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>38253000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>39679600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>37278900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36165800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36441600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34414800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>33109200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>30071200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>30500000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>29739700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>28710900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>29853200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>28796500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>31169400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>29666700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>29549200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1929200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1835700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1632700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1681400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1418400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1474500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1651200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1350100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1354800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>964200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1226200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1188200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>756600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>69900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3210900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>974000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3419900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2092300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1555600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1640000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>927300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1472400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1185400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>888500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>500100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1194800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>890400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1187900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1115500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1122400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1201900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1119400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>903300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>690600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>877400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>995800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>925700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1107800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1006400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E83" s="3">
         <v>179500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>177600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-109100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>183200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>180400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>189100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-37400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>202200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>210900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>166500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-129800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>168500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>167000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>269400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>260200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>253500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>246500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>250800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>271100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>260700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>266600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>264300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>280100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>269900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>280300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>274800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>200400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>194300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>191700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>183200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>167100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>170100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>170900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>163700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>171900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>157800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>167500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>165200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>160600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5057500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3026000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5406900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-615100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>903900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6636200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9613700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5121600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16676700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4098500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2694500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-371500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6815400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11788900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14592600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13014900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1452900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9143600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17094200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7726700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7785900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18230100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14904600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-15615000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>18266000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>28556200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8491100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>14152600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7409200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3516500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4908400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2922700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4933800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-668500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6120400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3166600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-175600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-454800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>6138900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-7659300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-407700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-349700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-283100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>363900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-292600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-317700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-266700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-310000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-299000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-237900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-293000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-799900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-144400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-149000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-367000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-488000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-363000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-328000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-269000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-298000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-242000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-65300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-87100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-97500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-81600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-136400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-92800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-73100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-70100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-117700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-40700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-48400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-99000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-55800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-255100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-222800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-52200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9072100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9976300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>219700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1432200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-81700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3337600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5069400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6139900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3731200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1308900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9431300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4070200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2954200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9813400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4477000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2442100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-834300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1356600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19525300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1167400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2971800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4549500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-578200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>44100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8682200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9589400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6665900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6075200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4803300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1151700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3260200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2613900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1395700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4649200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>218800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>463600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1338100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>392600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1913700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>397900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,8 +10427,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10239,86 +10472,89 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-466000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-405200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-407900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-410800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-502400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-508900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-514100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-505300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-512100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-347400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-339600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-546400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-502400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-559000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-544800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-531900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-505800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-482500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-483300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-485500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-469600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-471800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-424200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-308100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-311100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-421800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,370 +10925,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>20341900</v>
+      </c>
+      <c r="E100" s="3">
         <v>10658100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4542100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7897900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5852100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9451300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8163400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4257600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16555800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5669400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10789400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>266400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14735300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5112400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1975000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>901500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1916200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4250800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4582300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1057000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-769600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2259300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1877900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>985800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4691100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>183700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4469300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-519300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>669300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>786000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2933800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>393900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>426100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>523200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>695100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2004200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>948900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>46900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1561800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1975900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1878700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1330700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>69600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>154200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>910900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1111500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1779100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1168500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1018400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-411600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1565600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-154500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-99100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-404100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1555900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-146300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-92300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>675400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-626700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>588100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1371800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-672800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-256900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1061800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1143800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>241000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>133300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-817600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>317200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>74800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-87300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>852200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-663800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>692900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1633500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1128500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-774400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>603100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7316400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2612400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-78100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6348700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4895400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8031400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7850400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6934300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3697900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3790700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2447900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2396200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9705700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-25696300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11686500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13030200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-517300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14658700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-31361800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6989600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10939200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19148400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11775700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-14842100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3830900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20294300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2403000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7691400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2457600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3565000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1287100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>777600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3876900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3942400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>6370400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>18600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2198400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1113200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1863700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-4682400</v>
       </c>
     </row>
